--- a/must_be_sent_to_parse/assets_and_systems.xlsx
+++ b/must_be_sent_to_parse/assets_and_systems.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heidar\Documents\GitHub\RCM_data_concatinating\must_be_sent_to_parse\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h.alavi\Documents\GitHub\RCM_data_concatinating\must_be_sent_to_parse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B937EA9-0154-479E-B17A-211E69AEED7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49F4AA02-E580-4A94-9DC0-876F5679AE2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{33B5611C-7F48-4786-9A5F-04559DD55C0D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{33B5611C-7F48-4786-9A5F-04559DD55C0D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6883,10 +6883,10 @@
     <t>سیستم تصفیه آب آشامیدنی و کلر زنی</t>
   </si>
   <si>
-    <t>system</t>
-  </si>
-  <si>
-    <t>MANITORINGROOM2A01</t>
+    <t>Monitoring Room</t>
+  </si>
+  <si>
+    <t>نام سیستم</t>
   </si>
 </sst>
 </file>
@@ -6948,7 +6948,7 @@
     <tableColumn id="1" xr3:uid="{89B4C7F3-5838-47AD-8FB2-941BBC8B3416}" name="AssetNumber شماره دستگاه "/>
     <tableColumn id="2" xr3:uid="{3A7C7DCD-1CF2-4737-AF9D-191350A7864B}" name=" APP TagNo"/>
     <tableColumn id="3" xr3:uid="{8E95EC76-8892-4FC7-9C27-FCF723C10698}" name="AssetDescription نام دستگاه"/>
-    <tableColumn id="4" xr3:uid="{657B3AF4-879E-4CC6-81ED-982EBC002427}" name="system"/>
+    <tableColumn id="4" xr3:uid="{657B3AF4-879E-4CC6-81ED-982EBC002427}" name="نام سیستم"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7255,9 +7255,9 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="26.140625" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" customWidth="1"/>
+    <col min="4" max="4" width="25.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -7271,7 +7271,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -11205,7 +11205,7 @@
         <v>608</v>
       </c>
       <c r="D282" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
